--- a/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
+++ b/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/19_other_Oligo/00_check_Oligo_markers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louise.huuki/Library/CloudStorage/OneDrive-LieberInstituteforBrainDevelopment/LIBD_code/LFF_spatial_ERC/processed-data/19_other_Oligo/00_check_Oligo_markers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4CA557B-CECE-284A-AD23-6932FBA0C165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FB8189-DB5F-6A45-915D-F6D9EDA4EB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="1020" windowWidth="26620" windowHeight="15040" activeTab="1" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
+    <workbookView xWindow="1020" yWindow="1060" windowWidth="28960" windowHeight="16600" activeTab="1" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="134">
   <si>
     <t>rank</t>
   </si>
@@ -144,9 +147,6 @@
     <t>RBFOX1</t>
   </si>
   <si>
-    <t>LINGO2</t>
-  </si>
-  <si>
     <t>ARHGEF3</t>
   </si>
   <si>
@@ -160,13 +160,341 @@
   </si>
   <si>
     <t>RASGRF1 + RBFOX1</t>
+  </si>
+  <si>
+    <t>cellType</t>
+  </si>
+  <si>
+    <t>MeanRatio_Oligo</t>
+  </si>
+  <si>
+    <t>Enrichment_Oligo</t>
+  </si>
+  <si>
+    <t>MeanRatio_OligoOPC</t>
+  </si>
+  <si>
+    <t>Enrichment_OligoOPC</t>
+  </si>
+  <si>
+    <t>multiHit</t>
+  </si>
+  <si>
+    <t>OPALIN,SEMA6D,FIGN,LRP6,ABCG1,LINC01608,PPP3CA,LINC03048,ANO4,TNIK</t>
+  </si>
+  <si>
+    <t>ERBB4,GOLGA7,EMC10,OPALIN,ANK3,SEMA6D,OMG,ENOX1,GPRC5B,PRKACB</t>
+  </si>
+  <si>
+    <t>OPALIN,LRP6,ABCG1,LINC01608,LINC03048,ANO4,PLXDC2,MAPT,QDPR,CCNH</t>
+  </si>
+  <si>
+    <t>EMC10,OMG,PRKACB,KBTBD3,SYT11,SAR1B,CDC42BPA,MARCHF1,NUP133,CLASP2</t>
+  </si>
+  <si>
+    <t>ABCG1,ANO4,EMC10,LINC01608,LINC03048,LRP6,OMG,OPALIN,PRKACB,SEMA6D</t>
+  </si>
+  <si>
+    <t>ANKRD18A,LINC01877,ITGAV,ENSG00000258342,DPYSL5,PPP2R2C,SLC5A11,RASGRF2,CRYBG3,EEPD1</t>
+  </si>
+  <si>
+    <t>MTX2,LINC00609,ITGAV,ZDHHC14,RASGRF2,CEP170,CPXM2,KIF5C,S100B,ACTN2</t>
+  </si>
+  <si>
+    <t>ANKRD18A,LINC01877,ENSG00000258342,DPYSL5,PPP2R2C,SLC5A11,RASGRF2,CRYBG3,EEPD1,LRRC63</t>
+  </si>
+  <si>
+    <t>CEP170,KIF5C,ACTN2,CPXM2,MTX2,KCTD8,S100B,GAS2,LMCD1-AS1,LGR4</t>
+  </si>
+  <si>
+    <t>ACTN2,ANKRD18A,CEP170,CPXM2,CRYBG3,DPYSL5,EEPD1,ENSG00000258342,ITGAV,KIF5C,LINC01877,MTX2,PPP2R2C,RASGRF2,S100B,SLC5A11</t>
+  </si>
+  <si>
+    <t>MT-CO3,CNTNAP2</t>
+  </si>
+  <si>
+    <t>GPM6A,KCNJ3,KCND2,LINGO2,NTRK3,ADGRV1,MYT1L,NR2F1-AS1,GRIK1,SLC1A2</t>
+  </si>
+  <si>
+    <t>MT-CO3</t>
+  </si>
+  <si>
+    <t>LINGO2,SLC12A5,SYT1,AQP4,KCNC2,SRRM2,CAMKV,FBLN1,MGAT4C,ELAVL2</t>
+  </si>
+  <si>
+    <t>LINGO2,MT-CO3</t>
+  </si>
+  <si>
+    <t>ARHGEF3,ADGRF5,PRKCH,ABCG2,ATP10A,ABCB1,FLI1,CLDN5,EPAS1,ST8SIA6</t>
+  </si>
+  <si>
+    <t>ADGRF5,PRKCH,ATP10A,FLI1,CLDN5,ABCB1,ST8SIA6,MECOM,SLFN12L,ARHGEF3</t>
+  </si>
+  <si>
+    <t>ABCB1,ADGRF5,ARHGEF3,ATP10A,CLDN5,FLI1,PRKCH,ST8SIA6</t>
+  </si>
+  <si>
+    <t>ENSG00000286778,ENSG00000287550,GALR1,PLAAT1,ENSG00000278254,ENSG00000264015,STK32A,MYT1,SPRY4,COL9A1</t>
+  </si>
+  <si>
+    <t>LRRC4C,REV3L,NOVA1,CCDC50,DISC1,USP24,EPN2,OPHN1,NLGN4X,CASK</t>
+  </si>
+  <si>
+    <t>LINGO2, MT-CO3, GPM6A, KCNJ3, KCND2</t>
+  </si>
+  <si>
+    <t>KCTD1, LAMA2</t>
+  </si>
+  <si>
+    <t>Green2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oli.1, Oli.2, Oli.7, Oli.8, Oli.12 </t>
+  </si>
+  <si>
+    <t>Oli.9, MFOL</t>
+  </si>
+  <si>
+    <t>Oli.9, Oli.3</t>
+  </si>
+  <si>
+    <t>Annotation</t>
+  </si>
+  <si>
+    <t>Newly formed Oligo</t>
+  </si>
+  <si>
+    <t>perivascular Oligo</t>
+  </si>
+  <si>
+    <t>Mature RASGFR1</t>
+  </si>
+  <si>
+    <t>pseudotime rank</t>
+  </si>
+  <si>
+    <t>Sadick2022 Integrated Data</t>
+  </si>
+  <si>
+    <t>Study</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Subtypes</t>
+  </si>
+  <si>
+    <t>N nuclei</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Marques et al. (2016) </t>
+  </si>
+  <si>
+    <t>Adult + juvenile mouse</t>
+  </si>
+  <si>
+    <t>OPC, COP, NFOL, MFOL, MOL </t>
+  </si>
+  <si>
+    <t>5k Oligos</t>
+  </si>
+  <si>
+    <t>Jakel et al. (2019)</t>
+  </si>
+  <si>
+    <t>5 Ctrl, 4 MS</t>
+  </si>
+  <si>
+    <t>OPC, COP, ImOLs, Oligo</t>
+  </si>
+  <si>
+    <t>White matter</t>
+  </si>
+  <si>
+    <t>Mathys et al. (2019)</t>
+  </si>
+  <si>
+    <t>24 Ctrl, 24 AD</t>
+  </si>
+  <si>
+    <t>5 subclusters</t>
+  </si>
+  <si>
+    <t>80k (18k Oligos)</t>
+  </si>
+  <si>
+    <t>Prefrontal cortex</t>
+  </si>
+  <si>
+    <t>Sadick et al. (2022)</t>
+  </si>
+  <si>
+    <t>Ctrl, AD</t>
+  </si>
+  <si>
+    <t>Grubman et al. (2019)</t>
+  </si>
+  <si>
+    <t>6 Ctrl, 6 AD</t>
+  </si>
+  <si>
+    <t>6 subclusters (some AD or control specific)</t>
+  </si>
+  <si>
+    <t>ERC</t>
+  </si>
+  <si>
+    <t>4 Ctrl</t>
+  </si>
+  <si>
+    <t>2 clusters Oligo1 (OPALIN), Oligo2 (RBFOX1); 15 subclusters</t>
+  </si>
+  <si>
+    <t>Mathys et al. (2024)</t>
+  </si>
+  <si>
+    <t>48 Ctrl, 48 AD</t>
+  </si>
+  <si>
+    <t>OPALIN+ and RASGRF1+</t>
+  </si>
+  <si>
+    <t>Green et al. (2024)</t>
+  </si>
+  <si>
+    <t>n nuclei</t>
+  </si>
+  <si>
+    <t>18k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8k </t>
+  </si>
+  <si>
+    <t>80k</t>
+  </si>
+  <si>
+    <t>Sadick et al. (2022) integrated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 subclusters, </t>
+  </si>
+  <si>
+    <t>6 subclusters</t>
+  </si>
+  <si>
+    <t>23k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New data (PFC) Integrated </t>
+  </si>
+  <si>
+    <t>Zhou, Grubman, Manthys</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>596k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13k </t>
+  </si>
+  <si>
+    <r>
+      <t>10 regions including temporal cortex (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ERC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), 606 samples</t>
+    </r>
+  </si>
+  <si>
+    <t>1.3 M (221k ERC)</t>
+  </si>
+  <si>
+    <t>408k Oligo</t>
+  </si>
+  <si>
+    <r>
+      <t>ERC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, HC, TH, AG, PFC</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (283 samples)</t>
+    </r>
+  </si>
+  <si>
+    <t>Siletti et al. (2023)
+Allen brain atlas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPC(3 subcluster), COP, Oli (12 subcluster) </t>
+  </si>
+  <si>
+    <t>compare to ERC</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>check markes</t>
+  </si>
+  <si>
+    <t>marker stat correlation</t>
+  </si>
+  <si>
+    <t>Ctrl AD (437 total)</t>
+  </si>
+  <si>
+    <t>1.65M</t>
+  </si>
+  <si>
+    <t>346k Oligo, 62k OPC</t>
+  </si>
+  <si>
+    <t>prefromal cortex</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -179,6 +507,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -216,9 +557,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,57 +928,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8118FE2-0B82-7D4D-BDF4-7C654142C9BA}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="9.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>23</v>
@@ -611,139 +997,172 @@
       <c r="H2" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="2">
         <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="J7" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1" xr:uid="{C8118FE2-0B82-7D4D-BDF4-7C654142C9BA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B7">
-      <sortCondition ref="A1:A7"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -751,6 +1170,487 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A010F79-2158-CA4E-B969-AC78B6395658}">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13A16D39-6841-F047-89DE-86D42A4C45CC}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="36.5" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.5" customWidth="1"/>
+    <col min="6" max="6" width="34.5" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="136" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{13A16D39-6841-F047-89DE-86D42A4C45CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G7">
+      <sortCondition ref="A1:A7"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530D98AF-EB06-274A-9CD9-51E933ED3CBF}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
+++ b/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
@@ -1,28 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louise.huuki/Library/CloudStorage/OneDrive-LieberInstituteforBrainDevelopment/LIBD_code/LFF_spatial_ERC/processed-data/19_other_Oligo/00_check_Oligo_markers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/19_other_Oligo/00_check_Oligo_markers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FB8189-DB5F-6A45-915D-F6D9EDA4EB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{45DC2D14-E444-3940-B2F7-9E131A33B774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CABC204F-7EA9-F945-9022-D013B298D950}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1060" windowWidth="28960" windowHeight="16600" activeTab="1" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
+    <workbookView xWindow="640" yWindow="760" windowWidth="28540" windowHeight="17400" activeTab="1" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="Oligo Annotations" sheetId="1" r:id="rId1"/>
+    <sheet name="External Datasets" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oligo Annotations'!$A$1:$A$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,13 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="134">
-  <si>
-    <t>rank</t>
-  </si>
-  <si>
-    <t>Oligo</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="139">
   <si>
     <t>OPC</t>
   </si>
@@ -123,9 +114,6 @@
     <t>S0/S2</t>
   </si>
   <si>
-    <t>Sadick2022_int</t>
-  </si>
-  <si>
     <t>Int0/Int3</t>
   </si>
   <si>
@@ -144,9 +132,6 @@
     <t>PDGFRA</t>
   </si>
   <si>
-    <t>RBFOX1</t>
-  </si>
-  <si>
     <t>ARHGEF3</t>
   </si>
   <si>
@@ -162,84 +147,6 @@
     <t>RASGRF1 + RBFOX1</t>
   </si>
   <si>
-    <t>cellType</t>
-  </si>
-  <si>
-    <t>MeanRatio_Oligo</t>
-  </si>
-  <si>
-    <t>Enrichment_Oligo</t>
-  </si>
-  <si>
-    <t>MeanRatio_OligoOPC</t>
-  </si>
-  <si>
-    <t>Enrichment_OligoOPC</t>
-  </si>
-  <si>
-    <t>multiHit</t>
-  </si>
-  <si>
-    <t>OPALIN,SEMA6D,FIGN,LRP6,ABCG1,LINC01608,PPP3CA,LINC03048,ANO4,TNIK</t>
-  </si>
-  <si>
-    <t>ERBB4,GOLGA7,EMC10,OPALIN,ANK3,SEMA6D,OMG,ENOX1,GPRC5B,PRKACB</t>
-  </si>
-  <si>
-    <t>OPALIN,LRP6,ABCG1,LINC01608,LINC03048,ANO4,PLXDC2,MAPT,QDPR,CCNH</t>
-  </si>
-  <si>
-    <t>EMC10,OMG,PRKACB,KBTBD3,SYT11,SAR1B,CDC42BPA,MARCHF1,NUP133,CLASP2</t>
-  </si>
-  <si>
-    <t>ABCG1,ANO4,EMC10,LINC01608,LINC03048,LRP6,OMG,OPALIN,PRKACB,SEMA6D</t>
-  </si>
-  <si>
-    <t>ANKRD18A,LINC01877,ITGAV,ENSG00000258342,DPYSL5,PPP2R2C,SLC5A11,RASGRF2,CRYBG3,EEPD1</t>
-  </si>
-  <si>
-    <t>MTX2,LINC00609,ITGAV,ZDHHC14,RASGRF2,CEP170,CPXM2,KIF5C,S100B,ACTN2</t>
-  </si>
-  <si>
-    <t>ANKRD18A,LINC01877,ENSG00000258342,DPYSL5,PPP2R2C,SLC5A11,RASGRF2,CRYBG3,EEPD1,LRRC63</t>
-  </si>
-  <si>
-    <t>CEP170,KIF5C,ACTN2,CPXM2,MTX2,KCTD8,S100B,GAS2,LMCD1-AS1,LGR4</t>
-  </si>
-  <si>
-    <t>ACTN2,ANKRD18A,CEP170,CPXM2,CRYBG3,DPYSL5,EEPD1,ENSG00000258342,ITGAV,KIF5C,LINC01877,MTX2,PPP2R2C,RASGRF2,S100B,SLC5A11</t>
-  </si>
-  <si>
-    <t>MT-CO3,CNTNAP2</t>
-  </si>
-  <si>
-    <t>GPM6A,KCNJ3,KCND2,LINGO2,NTRK3,ADGRV1,MYT1L,NR2F1-AS1,GRIK1,SLC1A2</t>
-  </si>
-  <si>
-    <t>MT-CO3</t>
-  </si>
-  <si>
-    <t>LINGO2,SLC12A5,SYT1,AQP4,KCNC2,SRRM2,CAMKV,FBLN1,MGAT4C,ELAVL2</t>
-  </si>
-  <si>
-    <t>LINGO2,MT-CO3</t>
-  </si>
-  <si>
-    <t>ARHGEF3,ADGRF5,PRKCH,ABCG2,ATP10A,ABCB1,FLI1,CLDN5,EPAS1,ST8SIA6</t>
-  </si>
-  <si>
-    <t>ADGRF5,PRKCH,ATP10A,FLI1,CLDN5,ABCB1,ST8SIA6,MECOM,SLFN12L,ARHGEF3</t>
-  </si>
-  <si>
-    <t>ABCB1,ADGRF5,ARHGEF3,ATP10A,CLDN5,FLI1,PRKCH,ST8SIA6</t>
-  </si>
-  <si>
-    <t>ENSG00000286778,ENSG00000287550,GALR1,PLAAT1,ENSG00000278254,ENSG00000264015,STK32A,MYT1,SPRY4,COL9A1</t>
-  </si>
-  <si>
-    <t>LRRC4C,REV3L,NOVA1,CCDC50,DISC1,USP24,EPN2,OPHN1,NLGN4X,CASK</t>
-  </si>
-  <si>
     <t>LINGO2, MT-CO3, GPM6A, KCNJ3, KCND2</t>
   </si>
   <si>
@@ -262,12 +169,6 @@
   </si>
   <si>
     <t>Newly formed Oligo</t>
-  </si>
-  <si>
-    <t>perivascular Oligo</t>
-  </si>
-  <si>
-    <t>Mature RASGFR1</t>
   </si>
   <si>
     <t>pseudotime rank</t>
@@ -488,6 +389,117 @@
   </si>
   <si>
     <t>prefromal cortex</t>
+  </si>
+  <si>
+    <t>n donors</t>
+  </si>
+  <si>
+    <t>subtype OPALIN</t>
+  </si>
+  <si>
+    <t>subtype RASGRF1</t>
+  </si>
+  <si>
+    <t>subtype RBFOX1</t>
+  </si>
+  <si>
+    <t>Oligo6 (immature)</t>
+  </si>
+  <si>
+    <t>Oligo1 (mature)</t>
+  </si>
+  <si>
+    <t>S1*</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>Int4</t>
+  </si>
+  <si>
+    <t>Oligo1, Oligo5*</t>
+  </si>
+  <si>
+    <t>Int3, Int5</t>
+  </si>
+  <si>
+    <t>Oligo OPALIN</t>
+  </si>
+  <si>
+    <t>Oligo RASGRF1</t>
+  </si>
+  <si>
+    <t>Oligo RASGRF1*</t>
+  </si>
+  <si>
+    <t>Oligo1</t>
+  </si>
+  <si>
+    <t>Oligo.2 ("mature/end state"), OPC*, COP*</t>
+  </si>
+  <si>
+    <t>o5, o6</t>
+  </si>
+  <si>
+    <t>o3, o4</t>
+  </si>
+  <si>
+    <t>MFOL* (myelin forming)</t>
+  </si>
+  <si>
+    <t>Oli.5</t>
+  </si>
+  <si>
+    <t>Oli12, OPC1*, Oli5*</t>
+  </si>
+  <si>
+    <t>Late Oligo</t>
+  </si>
+  <si>
+    <t>Perivascular Oligo</t>
+  </si>
+  <si>
+    <t>RBFOX1, PDGFRA</t>
+  </si>
+  <si>
+    <t>OPALIN, OMG</t>
+  </si>
+  <si>
+    <t>Myelinating Oligo</t>
+  </si>
+  <si>
+    <t>Macnair et al. (2025)</t>
+  </si>
+  <si>
+    <t>632k</t>
+  </si>
+  <si>
+    <t>Ctrl, Multiple sclerosis</t>
+  </si>
+  <si>
+    <t>OPC (2 subclusters), COP, Oligo (7 subclusters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cortical heimsphere white and gray matter, WM &amp; GM lesions </t>
+  </si>
+  <si>
+    <t>Oligo_D</t>
+  </si>
+  <si>
+    <t>Oligo_A, Oligo_B</t>
+  </si>
+  <si>
+    <t>Oligo_C*, Oligo_D*</t>
+  </si>
+  <si>
+    <t>Oligo subtype</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>check markers</t>
   </si>
 </sst>
 </file>
@@ -557,7 +569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -566,23 +578,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -591,14 +593,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -944,222 +964,222 @@
   <sheetData>
     <row r="1" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>72</v>
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>65</v>
+        <v>125</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1171,535 +1191,417 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A010F79-2158-CA4E-B969-AC78B6395658}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" customWidth="1"/>
+    <col min="6" max="6" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="6">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="G3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="6">
+        <v>48</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="6">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="6">
+        <v>96</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="6">
+        <v>437</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="6">
         <v>80</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" t="b">
+      <c r="C11" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="I11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="G10" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="J11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>129</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="H2:H11">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>$H$3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>$H$3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13A16D39-6841-F047-89DE-86D42A4C45CC}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="36.5" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" customWidth="1"/>
-    <col min="5" max="5" width="31.5" customWidth="1"/>
-    <col min="6" max="6" width="34.5" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="221" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{13A16D39-6841-F047-89DE-86D42A4C45CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G7">
-      <sortCondition ref="A1:A7"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530D98AF-EB06-274A-9CD9-51E933ED3CBF}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
 </file>
--- a/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
+++ b/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/19_other_Oligo/00_check_Oligo_markers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{45DC2D14-E444-3940-B2F7-9E131A33B774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CABC204F-7EA9-F945-9022-D013B298D950}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{45DC2D14-E444-3940-B2F7-9E131A33B774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E80A66AE-3A5B-724E-ABEB-E4A05E451D84}"/>
   <bookViews>
-    <workbookView xWindow="640" yWindow="760" windowWidth="28540" windowHeight="17400" activeTab="1" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
   </bookViews>
   <sheets>
     <sheet name="Oligo Annotations" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="146">
   <si>
     <t>OPC</t>
   </si>
@@ -500,6 +500,27 @@
   </si>
   <si>
     <t>check markers</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.neuron.2024.11.016</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>Annotation_short</t>
+  </si>
+  <si>
+    <t>Oligo.NF</t>
+  </si>
+  <si>
+    <t>Oligo.M</t>
+  </si>
+  <si>
+    <t>Oligo.L</t>
+  </si>
+  <si>
+    <t>Oligo.P</t>
   </si>
 </sst>
 </file>
@@ -629,6 +650,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -948,21 +973,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8118FE2-0B82-7D4D-BDF4-7C654142C9BA}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+    <col min="2" max="3" width="15.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
@@ -970,49 +995,52 @@
         <v>41</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>21</v>
@@ -1021,164 +1049,182 @@
         <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="2">
         <v>2</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="2">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="2">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1191,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A010F79-2158-CA4E-B969-AC78B6395658}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
@@ -1200,15 +1246,16 @@
     <col min="4" max="4" width="58" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.1640625" customWidth="1"/>
     <col min="6" max="6" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="54.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>45</v>
       </c>
@@ -1228,25 +1275,28 @@
         <v>48</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>50</v>
       </c>
@@ -1261,15 +1311,16 @@
       <c r="F2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="b">
+      <c r="G2" s="6"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>54</v>
       </c>
@@ -1288,26 +1339,27 @@
       <c r="F3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="3" t="b">
+      <c r="I3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>58</v>
       </c>
@@ -1326,18 +1378,19 @@
       <c r="F4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="3" t="b">
+      <c r="I4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>63</v>
       </c>
@@ -1354,26 +1407,27 @@
       <c r="F5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H5" s="3" t="b">
+      <c r="I5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>79</v>
       </c>
@@ -1386,26 +1440,27 @@
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M6" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>65</v>
       </c>
@@ -1424,26 +1479,27 @@
       <c r="F7" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6"/>
+      <c r="H7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="3" t="b">
+      <c r="I7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>92</v>
       </c>
@@ -1462,26 +1518,27 @@
       <c r="F8" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H8" s="3" t="b">
+      <c r="I8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>71</v>
       </c>
@@ -1500,26 +1557,27 @@
       <c r="F9" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6"/>
+      <c r="H9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="3" t="b">
+      <c r="I9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>74</v>
       </c>
@@ -1538,26 +1596,27 @@
       <c r="F10" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H10" s="3" t="b">
+      <c r="I10" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>128</v>
       </c>
@@ -1573,33 +1632,36 @@
       <c r="E11" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="H11" s="3" t="b">
+      <c r="I11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>133</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="H2:H11">
+  <conditionalFormatting sqref="I2:I11">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>$H$3</formula>
+      <formula>$I$3</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>$H$3</formula>
+      <formula>$I$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
+++ b/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/19_other_Oligo/00_check_Oligo_markers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{45DC2D14-E444-3940-B2F7-9E131A33B774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E80A66AE-3A5B-724E-ABEB-E4A05E451D84}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{45DC2D14-E444-3940-B2F7-9E131A33B774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1635038-D87A-DB4B-80EF-B5A95C4CCB6C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
+    <workbookView xWindow="44520" yWindow="1720" windowWidth="30240" windowHeight="17800" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
   </bookViews>
   <sheets>
     <sheet name="Oligo Annotations" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="146">
   <si>
     <t>OPC</t>
   </si>
@@ -973,21 +973,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8118FE2-0B82-7D4D-BDF4-7C654142C9BA}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" style="3" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
@@ -1004,25 +1005,28 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1039,11 +1043,9 @@
         <v>29</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>21</v>
@@ -1052,10 +1054,13 @@
         <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1071,26 +1076,29 @@
       <c r="E3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1">
+        <v>8587</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1104,26 +1112,29 @@
         <v>2</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="1">
+        <v>4254</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1139,26 +1150,29 @@
       <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="1">
+        <v>6911</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1174,26 +1188,29 @@
       <c r="E6" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="1">
+        <v>12519</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -1209,22 +1226,25 @@
       <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="1">
+        <v>12010</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
     </row>

--- a/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
+++ b/processed-data/19_other_Oligo/00_check_Oligo_markers/ERC_Oligo_notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/19_other_Oligo/00_check_Oligo_markers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{45DC2D14-E444-3940-B2F7-9E131A33B774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1635038-D87A-DB4B-80EF-B5A95C4CCB6C}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{45DC2D14-E444-3940-B2F7-9E131A33B774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{421F8BEA-9673-434A-9427-D6525E516265}"/>
   <bookViews>
-    <workbookView xWindow="44520" yWindow="1720" windowWidth="30240" windowHeight="17800" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
+    <workbookView xWindow="38400" yWindow="1720" windowWidth="30240" windowHeight="17800" xr2:uid="{D3C45F6A-23E9-DF44-BEE0-E5DD3B4BB180}"/>
   </bookViews>
   <sheets>
     <sheet name="Oligo Annotations" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="148">
   <si>
     <t>OPC</t>
   </si>
@@ -520,7 +520,13 @@
     <t>Oligo.L</t>
   </si>
   <si>
-    <t>Oligo.P</t>
+    <t>Oligo.PM</t>
+  </si>
+  <si>
+    <t>Oligo.PV</t>
+  </si>
+  <si>
+    <t>Pre-myelinating Oligo</t>
   </si>
 </sst>
 </file>
@@ -650,10 +656,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -977,7 +979,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
-    <col min="2" max="3" width="15.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="3" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
@@ -1106,7 +1109,7 @@
         <v>124</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -1139,10 +1142,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
